--- a/VerveStacks_KEN/vt_vervestacks_KEN_v1.xlsx
+++ b/VerveStacks_KEN/vt_vervestacks_KEN_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1B2AF98-AC0C-4B78-B7DF-329E0C249510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D26D12F-734B-44C5-9676-04231129C135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{19FD255E-6EDB-4B51-B3F9-12CF5ADC9DE0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{43E3E248-B7C6-484C-8696-61CE90A02E36}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1141,7 +1141,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08AED9EF-6325-47F1-9956-D610D81222B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54228454-590B-475C-81F9-279A362FA92B}">
   <dimension ref="B9:T18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1663,7 +1663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EF68DAE-FE78-4C92-8E57-FF31BFDD41F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BA70E8-B602-4579-B3A7-1E6F0345A227}">
   <dimension ref="B9:T50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3878,7 +3878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22C1B7C-AC29-4531-B239-E93308747A4A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46EE760D-CA3E-48DA-AA57-6CB91C2F3393}">
   <dimension ref="B9:T73"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6292,7 +6292,7 @@
         <v>33</v>
       </c>
       <c r="L55">
-        <v>0.23864191972779222</v>
+        <v>0.2386419197277922</v>
       </c>
       <c r="N55" t="s">
         <v>97</v>
@@ -6339,7 +6339,7 @@
         <v>33</v>
       </c>
       <c r="L56">
-        <v>0.23864191972779222</v>
+        <v>0.2386419197277922</v>
       </c>
       <c r="N56" t="s">
         <v>97</v>
@@ -6386,7 +6386,7 @@
         <v>33</v>
       </c>
       <c r="L57">
-        <v>0.23864191972779222</v>
+        <v>0.2386419197277922</v>
       </c>
       <c r="N57" t="s">
         <v>97</v>
@@ -7228,7 +7228,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEF99D3E-831C-4913-8CD9-3B02C8B130DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76C6D02E-433E-47B1-9949-D28DB6F52FDD}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
